--- a/public/downloads/JiangModelling2021.xlsx
+++ b/public/downloads/JiangModelling2021.xlsx
@@ -8,30 +8,32 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="Allegro-OAM-L" sheetId="3" r:id="rId3"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="4" r:id="rId4"/>
-    <sheet name="CHGNetv0.3.0" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="NequIP-OAM-L" sheetId="12" r:id="rId12"/>
-    <sheet name="ORB-v3" sheetId="13" r:id="rId13"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="17" r:id="rId17"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Allegro-OAM-L" sheetId="5" r:id="rId5"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="6" r:id="rId6"/>
+    <sheet name="CHGNetv0.3.0" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="NequIP-OAM-L" sheetId="14" r:id="rId14"/>
+    <sheet name="ORB-v3" sheetId="15" r:id="rId15"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="19" r:id="rId19"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -63,10 +65,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -169,6 +171,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
@@ -657,10 +680,10 @@
         <v>25</v>
       </c>
       <c r="N3" s="5">
-        <v>587.8392851352692</v>
+        <v>587839.2851352692</v>
       </c>
       <c r="O3" s="4">
-        <v>0.08406110183544532</v>
+        <v>84.06110183544533</v>
       </c>
       <c r="P3" s="5">
         <v>6993</v>
@@ -707,10 +730,10 @@
         <v>25</v>
       </c>
       <c r="N4" s="5">
-        <v>406.7242591381073</v>
+        <v>406724.2591381073</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05273230379075682</v>
+        <v>52.73230379075682</v>
       </c>
       <c r="P4" s="5">
         <v>7713</v>
@@ -757,10 +780,10 @@
         <v>25</v>
       </c>
       <c r="N5" s="5">
-        <v>1129.042332410812</v>
+        <v>1129042.332410812</v>
       </c>
       <c r="O5" s="4">
-        <v>0.09671426523991883</v>
+        <v>96.71426523991883</v>
       </c>
       <c r="P5" s="5">
         <v>11674</v>
@@ -807,10 +830,10 @@
         <v>25</v>
       </c>
       <c r="N6" s="5">
-        <v>1033.346237182617</v>
+        <v>1033346.237182617</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1551803930293764</v>
+        <v>155.1803930293764</v>
       </c>
       <c r="P6" s="5">
         <v>6659</v>
@@ -857,10 +880,10 @@
         <v>24</v>
       </c>
       <c r="N7" s="5">
-        <v>3055.39971446991</v>
+        <v>3055399.71446991</v>
       </c>
       <c r="O7" s="4">
-        <v>0.5366941356876708</v>
+        <v>536.6941356876707</v>
       </c>
       <c r="P7" s="5">
         <v>5693</v>
@@ -907,10 +930,10 @@
         <v>25</v>
       </c>
       <c r="N8" s="5">
-        <v>290.7434782981873</v>
+        <v>290743.4782981873</v>
       </c>
       <c r="O8" s="4">
-        <v>0.04051609229350436</v>
+        <v>40.51609229350436</v>
       </c>
       <c r="P8" s="5">
         <v>7176</v>
@@ -957,10 +980,10 @@
         <v>25</v>
       </c>
       <c r="N9" s="5">
-        <v>488.6394865512848</v>
+        <v>488639.4865512848</v>
       </c>
       <c r="O9" s="4">
-        <v>0.06012544438923155</v>
+        <v>60.12544438923155</v>
       </c>
       <c r="P9" s="5">
         <v>8127</v>
@@ -1007,10 +1030,10 @@
         <v>25</v>
       </c>
       <c r="N10" s="5">
-        <v>830.2775039672852</v>
+        <v>830277.5039672852</v>
       </c>
       <c r="O10" s="4">
-        <v>0.101056171368949</v>
+        <v>101.056171368949</v>
       </c>
       <c r="P10" s="5">
         <v>8216</v>
@@ -1057,10 +1080,10 @@
         <v>25</v>
       </c>
       <c r="N11" s="5">
-        <v>495.9135842323303</v>
+        <v>495913.5842323303</v>
       </c>
       <c r="O11" s="4">
-        <v>0.07537826177721998</v>
+        <v>75.37826177721999</v>
       </c>
       <c r="P11" s="5">
         <v>6579</v>
@@ -1107,10 +1130,10 @@
         <v>25</v>
       </c>
       <c r="N12" s="5">
-        <v>759.602338552475</v>
+        <v>759602.338552475</v>
       </c>
       <c r="O12" s="4">
-        <v>0.1019190042335268</v>
+        <v>101.9190042335268</v>
       </c>
       <c r="P12" s="5">
         <v>7453</v>
@@ -1157,10 +1180,10 @@
         <v>25</v>
       </c>
       <c r="N13" s="5">
-        <v>367.3450756072998</v>
+        <v>367345.0756072998</v>
       </c>
       <c r="O13" s="4">
-        <v>0.04536804688246262</v>
+        <v>45.36804688246262</v>
       </c>
       <c r="P13" s="5">
         <v>8097</v>
@@ -1207,10 +1230,10 @@
         <v>25</v>
       </c>
       <c r="N14" s="5">
-        <v>521.9175667762756</v>
+        <v>521917.5667762756</v>
       </c>
       <c r="O14" s="4">
-        <v>0.07443205458874438</v>
+        <v>74.43205458874438</v>
       </c>
       <c r="P14" s="5">
         <v>7012</v>
@@ -1257,10 +1280,10 @@
         <v>25</v>
       </c>
       <c r="N15" s="5">
-        <v>6233.504547595978</v>
+        <v>6233504.547595978</v>
       </c>
       <c r="O15" s="4">
-        <v>0.8795688651892165</v>
+        <v>879.5688651892165</v>
       </c>
       <c r="P15" s="5">
         <v>7087</v>
@@ -1307,10 +1330,10 @@
         <v>25</v>
       </c>
       <c r="N16" s="5">
-        <v>4555.858403205872</v>
+        <v>4555858.403205872</v>
       </c>
       <c r="O16" s="4">
-        <v>0.8198413538250624</v>
+        <v>819.8413538250624</v>
       </c>
       <c r="P16" s="5">
         <v>5557</v>
@@ -1357,10 +1380,10 @@
         <v>25</v>
       </c>
       <c r="N17" s="5">
-        <v>1051.564282178879</v>
+        <v>1051564.282178879</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1605932013101525</v>
+        <v>160.5932013101525</v>
       </c>
       <c r="P17" s="5">
         <v>6548</v>
@@ -1407,10 +1430,10 @@
         <v>25</v>
       </c>
       <c r="N18" s="5">
-        <v>1034.124529361725</v>
+        <v>1034124.529361725</v>
       </c>
       <c r="O18" s="4">
-        <v>0.1693897672992178</v>
+        <v>169.3897672992179</v>
       </c>
       <c r="P18" s="5">
         <v>6105</v>
@@ -1438,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1449,9 +1472,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1485,8 +1514,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1508,50 +1545,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2028489787944572</v>
+        <v>0.1478650302724598</v>
       </c>
       <c r="C3" s="4">
-        <v>0.05082321189869132</v>
+        <v>0.06069019570808993</v>
       </c>
       <c r="D3" s="4">
-        <v>0.134880311516452</v>
+        <v>0.09742234539098479</v>
       </c>
       <c r="E3" s="4">
-        <v>28.99319727891157</v>
+        <v>31.04489795918367</v>
       </c>
       <c r="F3" s="4">
-        <v>47.38434004474272</v>
+        <v>50.80536912751678</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.06069019570808993</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1359606413606922</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03072176512878113</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1562,6 +1635,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1569,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1580,9 +1654,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1616,8 +1696,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1639,25 +1727,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1787252858797536</v>
+        <v>0.1868064651842765</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1422051132320797</v>
+        <v>0.1174892122467159</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1651147868112259</v>
+        <v>0.2194096613494999</v>
       </c>
       <c r="E3" s="4">
-        <v>31.47210884353736</v>
+        <v>29.16326530612245</v>
       </c>
       <c r="F3" s="4">
-        <v>55.48590604026845</v>
+        <v>54.25458612975378</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
@@ -1672,17 +1778,35 @@
         <v>14</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1174892122467159</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1565018064796635</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06650123187085689</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1693,6 +1817,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1700,7 +1825,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1711,9 +1836,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1747,8 +1878,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1770,50 +1909,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1178448855662649</v>
+        <v>0.2028489787944572</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08365671041864405</v>
+        <v>0.05082321189869132</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1036911688156434</v>
+        <v>0.134880311516452</v>
       </c>
       <c r="E3" s="4">
-        <v>27.20680272108846</v>
+        <v>28.99319727891157</v>
       </c>
       <c r="F3" s="4">
-        <v>52.99507829977628</v>
+        <v>47.38434004474272</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.05082321189869132</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1921688267988733</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03265333566829609</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1824,6 +1999,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1831,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1842,9 +2018,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1878,8 +2060,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1901,50 +2091,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1170939741344614</v>
+        <v>0.1787252858797536</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08828811473418455</v>
+        <v>0.1422051132320797</v>
       </c>
       <c r="D3" s="4">
-        <v>0.08881605966626299</v>
+        <v>0.1651147868112259</v>
       </c>
       <c r="E3" s="4">
-        <v>34.78367346938776</v>
+        <v>31.47210884353736</v>
       </c>
       <c r="F3" s="4">
-        <v>55.80581655480973</v>
+        <v>55.48590604026845</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
       </c>
       <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>14</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>14</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.0831060369197382</v>
+      </c>
+      <c r="O3" s="5">
         <v>11</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="P3" s="4">
+        <v>0.1660903117661232</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1159855670425376</v>
+      </c>
+      <c r="R3" s="5">
         <v>11</v>
       </c>
-      <c r="M3" s="5">
+      <c r="S3" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1955,6 +2181,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1962,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1973,9 +2200,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2009,8 +2242,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2032,25 +2273,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2479128628963084</v>
+        <v>0.1178448855662649</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2332502790722853</v>
+        <v>0.08365671041864405</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2427624477511684</v>
+        <v>0.1036911688156434</v>
       </c>
       <c r="E3" s="4">
-        <v>30.88299319727891</v>
+        <v>27.20680272108846</v>
       </c>
       <c r="F3" s="4">
-        <v>52.8814317673379</v>
+        <v>52.99507829977628</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
@@ -2073,9 +2332,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.07791603198902752</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09843941183832865</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04596941334595215</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2086,6 +2363,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2093,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2104,9 +2382,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2140,8 +2424,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2163,50 +2455,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2534777335205066</v>
+        <v>0.1170939741344614</v>
       </c>
       <c r="C3" s="4">
-        <v>0.117642376743738</v>
+        <v>0.08828811473418455</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1983704630964498</v>
+        <v>0.08881605966626299</v>
       </c>
       <c r="E3" s="4">
-        <v>22.66258503401358</v>
+        <v>34.78367346938776</v>
       </c>
       <c r="F3" s="4">
-        <v>48.60134228187921</v>
+        <v>55.80581655480973</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.06868355790376279</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1284989233651399</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08565917752053435</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2217,6 +2545,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2224,7 +2553,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2235,9 +2564,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2271,8 +2606,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2294,50 +2637,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1423700832700537</v>
+        <v>0.2479128628963084</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1182810018005842</v>
+        <v>0.2332502790722853</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1034702096874731</v>
+        <v>0.2427624477511684</v>
       </c>
       <c r="E3" s="4">
-        <v>36.66666666666666</v>
+        <v>30.88299319727891</v>
       </c>
       <c r="F3" s="4">
-        <v>57.63310961968691</v>
+        <v>52.8814317673379</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.2332502790722853</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09789509623748437</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02852958038640429</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2348,6 +2727,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2355,7 +2735,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2366,9 +2746,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2402,8 +2788,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2425,25 +2819,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2201447333125054</v>
+        <v>0.2534777335205066</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1068788938442919</v>
+        <v>0.117642376743738</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1865248357703823</v>
+        <v>0.1983704630964498</v>
       </c>
       <c r="E3" s="4">
-        <v>22.84897959183675</v>
+        <v>22.66258503401358</v>
       </c>
       <c r="F3" s="4">
-        <v>50.56241610738251</v>
+        <v>48.60134228187921</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
@@ -2458,17 +2870,33 @@
         <v>23</v>
       </c>
       <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>22</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
         <v>2</v>
       </c>
-      <c r="L3" s="5">
-        <v>21</v>
-      </c>
-      <c r="M3" s="5">
+      <c r="P3" s="4">
+        <v>0.2534777335205066</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.117642376743738</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2479,6 +2907,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2486,7 +2915,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2497,9 +2926,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2533,8 +2968,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2556,50 +2999,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.06666762978819495</v>
+        <v>0.1423700832700537</v>
       </c>
       <c r="C3" s="4">
-        <v>0.03776893141400591</v>
+        <v>0.1182810018005842</v>
       </c>
       <c r="D3" s="4">
-        <v>0.05533566304467122</v>
+        <v>0.1034702096874731</v>
       </c>
       <c r="E3" s="4">
-        <v>37.0639455782313</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="F3" s="4">
-        <v>58.87427293064892</v>
+        <v>57.63310961968691</v>
       </c>
       <c r="G3" s="5">
         <v>25</v>
       </c>
       <c r="H3" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1182810018005842</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1091525168368696</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04703682075704426</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2610,12 +3089,1282 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2201447333125054</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1068788938442919</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1865248357703823</v>
+      </c>
+      <c r="E3" s="4">
+        <v>22.84897959183675</v>
+      </c>
+      <c r="F3" s="4">
+        <v>50.56241610738251</v>
+      </c>
+      <c r="G3" s="5">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>23</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>21</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2201447333125054</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1068788938442919</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>88</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3277211829925005</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2897197544353641</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2878088150910777</v>
+      </c>
+      <c r="K3" s="4">
+        <v>26.1156462585034</v>
+      </c>
+      <c r="L3" s="4">
+        <v>49.81073825503356</v>
+      </c>
+      <c r="M3" s="5">
+        <v>25</v>
+      </c>
+      <c r="N3" s="5">
+        <v>587839.2851352692</v>
+      </c>
+      <c r="O3" s="4">
+        <v>84.06110183544533</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>76</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>76</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1273865862705376</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.04049534694279968</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.1272579340322585</v>
+      </c>
+      <c r="K4" s="4">
+        <v>28.75782312925169</v>
+      </c>
+      <c r="L4" s="4">
+        <v>51.10961968680089</v>
+      </c>
+      <c r="M4" s="5">
+        <v>25</v>
+      </c>
+      <c r="N4" s="5">
+        <v>406724.2591381073</v>
+      </c>
+      <c r="O4" s="4">
+        <v>52.73230379075682</v>
+      </c>
+      <c r="P4" s="5">
+        <v>7713</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>96</v>
+      </c>
+      <c r="E5" s="3">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.6374737633158065</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1156091104455186</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.363398820866928</v>
+      </c>
+      <c r="K5" s="4">
+        <v>13.20136054421768</v>
+      </c>
+      <c r="L5" s="4">
+        <v>21.65100671140941</v>
+      </c>
+      <c r="M5" s="5">
+        <v>25</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1129042.332410812</v>
+      </c>
+      <c r="O5" s="4">
+        <v>96.71426523991883</v>
+      </c>
+      <c r="P5" s="5">
+        <v>11674</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>96</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>96</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1215601623843719</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.0303974656869741</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1399826746361346</v>
+      </c>
+      <c r="K6" s="4">
+        <v>19.10204081632653</v>
+      </c>
+      <c r="L6" s="4">
+        <v>47.35838926174497</v>
+      </c>
+      <c r="M6" s="5">
+        <v>25</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1033346.237182617</v>
+      </c>
+      <c r="O6" s="4">
+        <v>155.1803930293764</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>75</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>75</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1195192300007945</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.04066710313548086</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.07658893911216026</v>
+      </c>
+      <c r="K7" s="4">
+        <v>28.90306122448981</v>
+      </c>
+      <c r="L7" s="4">
+        <v>54.13963460104452</v>
+      </c>
+      <c r="M7" s="5">
+        <v>24</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3055399.71446991</v>
+      </c>
+      <c r="O7" s="4">
+        <v>536.6941356876707</v>
+      </c>
+      <c r="P7" s="5">
+        <v>5693</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>72</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1359606413606922</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.03072176512878113</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.07709624232482215</v>
+      </c>
+      <c r="K8" s="4">
+        <v>31.04489795918367</v>
+      </c>
+      <c r="L8" s="4">
+        <v>50.80536912751678</v>
+      </c>
+      <c r="M8" s="5">
+        <v>25</v>
+      </c>
+      <c r="N8" s="5">
+        <v>290743.4782981873</v>
+      </c>
+      <c r="O8" s="4">
+        <v>40.51609229350436</v>
+      </c>
+      <c r="P8" s="5">
+        <v>7176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.1565018064796635</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.06650123187085689</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.1562062804762213</v>
+      </c>
+      <c r="K9" s="4">
+        <v>29.16326530612245</v>
+      </c>
+      <c r="L9" s="4">
+        <v>54.25458612975378</v>
+      </c>
+      <c r="M9" s="5">
+        <v>25</v>
+      </c>
+      <c r="N9" s="5">
+        <v>488639.4865512848</v>
+      </c>
+      <c r="O9" s="4">
+        <v>60.12544438923155</v>
+      </c>
+      <c r="P9" s="5">
+        <v>8127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>76</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>76</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1921688267988733</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.03265333566829609</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1138221176798819</v>
+      </c>
+      <c r="K10" s="4">
+        <v>28.99319727891157</v>
+      </c>
+      <c r="L10" s="4">
+        <v>47.38434004474272</v>
+      </c>
+      <c r="M10" s="5">
+        <v>25</v>
+      </c>
+      <c r="N10" s="5">
+        <v>830277.5039672852</v>
+      </c>
+      <c r="O10" s="4">
+        <v>101.056171368949</v>
+      </c>
+      <c r="P10" s="5">
+        <v>8216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1660903117661232</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1159855670425376</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1560887334993542</v>
+      </c>
+      <c r="K11" s="4">
+        <v>31.47210884353736</v>
+      </c>
+      <c r="L11" s="4">
+        <v>55.48590604026845</v>
+      </c>
+      <c r="M11" s="5">
+        <v>25</v>
+      </c>
+      <c r="N11" s="5">
+        <v>495913.5842323303</v>
+      </c>
+      <c r="O11" s="4">
+        <v>75.37826177721999</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6579</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>40</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>60</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>60</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.09843941183832865</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.04596941334595215</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.07778368301571571</v>
+      </c>
+      <c r="K12" s="4">
+        <v>27.20680272108846</v>
+      </c>
+      <c r="L12" s="4">
+        <v>52.99507829977628</v>
+      </c>
+      <c r="M12" s="5">
+        <v>25</v>
+      </c>
+      <c r="N12" s="5">
+        <v>759602.338552475</v>
+      </c>
+      <c r="O12" s="4">
+        <v>101.9190042335268</v>
+      </c>
+      <c r="P12" s="5">
+        <v>7453</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1284989233651399</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.08565917752053435</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1174183202073245</v>
+      </c>
+      <c r="K13" s="4">
+        <v>34.78367346938776</v>
+      </c>
+      <c r="L13" s="4">
+        <v>55.80581655480973</v>
+      </c>
+      <c r="M13" s="5">
+        <v>25</v>
+      </c>
+      <c r="N13" s="5">
+        <v>367345.0756072998</v>
+      </c>
+      <c r="O13" s="4">
+        <v>45.36804688246262</v>
+      </c>
+      <c r="P13" s="5">
+        <v>8097</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>40</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>60</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>60</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.09789509623748437</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.02852958038640429</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.08626457267954871</v>
+      </c>
+      <c r="K14" s="4">
+        <v>30.88299319727891</v>
+      </c>
+      <c r="L14" s="4">
+        <v>52.8814317673379</v>
+      </c>
+      <c r="M14" s="5">
+        <v>25</v>
+      </c>
+      <c r="N14" s="5">
+        <v>521917.5667762756</v>
+      </c>
+      <c r="O14" s="4">
+        <v>74.43205458874438</v>
+      </c>
+      <c r="P14" s="5">
+        <v>7012</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>92</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>88</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2534777335205066</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.117642376743738</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1983704630964498</v>
+      </c>
+      <c r="K15" s="4">
+        <v>22.66258503401358</v>
+      </c>
+      <c r="L15" s="4">
+        <v>48.60134228187921</v>
+      </c>
+      <c r="M15" s="5">
+        <v>25</v>
+      </c>
+      <c r="N15" s="5">
+        <v>6233504.547595978</v>
+      </c>
+      <c r="O15" s="4">
+        <v>879.5688651892165</v>
+      </c>
+      <c r="P15" s="5">
+        <v>7087</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>52</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>48</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1091525168368696</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.04703682075704426</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.0628565911374719</v>
+      </c>
+      <c r="K16" s="4">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="L16" s="4">
+        <v>57.63310961968691</v>
+      </c>
+      <c r="M16" s="5">
+        <v>25</v>
+      </c>
+      <c r="N16" s="5">
+        <v>4555858.403205872</v>
+      </c>
+      <c r="O16" s="4">
+        <v>819.8413538250624</v>
+      </c>
+      <c r="P16" s="5">
+        <v>5557</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>92</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3">
+        <v>84</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2201447333125054</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1068788938442919</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1865248357703823</v>
+      </c>
+      <c r="K17" s="4">
+        <v>22.84897959183675</v>
+      </c>
+      <c r="L17" s="4">
+        <v>50.56241610738251</v>
+      </c>
+      <c r="M17" s="5">
+        <v>25</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1051564.282178879</v>
+      </c>
+      <c r="O17" s="4">
+        <v>160.5932013101525</v>
+      </c>
+      <c r="P17" s="5">
+        <v>6548</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>44</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.06513474206140693</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.02839242812467254</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.05902947614612237</v>
+      </c>
+      <c r="K18" s="4">
+        <v>37.0639455782313</v>
+      </c>
+      <c r="L18" s="4">
+        <v>58.87427293064892</v>
+      </c>
+      <c r="M18" s="5">
+        <v>25</v>
+      </c>
+      <c r="N18" s="5">
+        <v>1034124.529361725</v>
+      </c>
+      <c r="O18" s="4">
+        <v>169.3897672992179</v>
+      </c>
+      <c r="P18" s="5">
+        <v>6105</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.06666762978819495</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.03776893141400591</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.05533566304467122</v>
+      </c>
+      <c r="E3" s="4">
+        <v>37.0639455782313</v>
+      </c>
+      <c r="F3" s="4">
+        <v>58.87427293064892</v>
+      </c>
+      <c r="G3" s="5">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>11</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>11</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.03098295096032214</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06513474206140693</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02839242812467254</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2820,13 +4569,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -2996,13 +4745,13 @@
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3260,13 +5009,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
       </c>
       <c r="N15" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3348,13 +5097,13 @@
         <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="25" customHeight="1">
@@ -3414,9 +5163,808 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>22</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>19</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>19</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>19</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>24</v>
+      </c>
+      <c r="E5" s="5">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>20</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>19</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>24</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>24</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>18</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>15</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>7</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>18</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>18</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>14</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>9</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>19</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>19</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>16</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>10</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>15</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>15</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>12</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>9</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>15</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>12</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>23</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>22</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>19</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>10</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>23</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5">
+        <v>21</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>19</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>14</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>11</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>11</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>8</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3427,9 +5975,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3463,8 +6017,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3486,10 +6048,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.3277211829925005</v>
@@ -3527,9 +6107,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3277211829925005</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2897197544353641</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3540,14 +6136,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3558,9 +6155,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3594,8 +6197,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3617,10 +6228,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.3123815856364589</v>
@@ -3658,9 +6287,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.2984004114507624</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1273865862705376</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04049534694279968</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3671,14 +6318,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3689,9 +6337,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3725,8 +6379,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3748,10 +6410,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.6374737633158065</v>
@@ -3789,9 +6469,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6374737633158065</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1156091104455186</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3802,14 +6498,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3820,9 +6517,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3856,8 +6559,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3879,10 +6590,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.1215601623843719</v>
@@ -3920,9 +6649,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1215601623843719</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0303974656869741</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3933,14 +6678,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3951,9 +6697,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3987,8 +6739,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4010,10 +6770,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.118767475309624</v>
@@ -4051,9 +6829,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.00902105629404574</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1195192300007945</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04066710313548086</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4064,268 +6860,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1478650302724598</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.06069019570808993</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.09742234539098479</v>
-      </c>
-      <c r="E3" s="4">
-        <v>31.04489795918367</v>
-      </c>
-      <c r="F3" s="4">
-        <v>50.80536912751678</v>
-      </c>
-      <c r="G3" s="5">
-        <v>25</v>
-      </c>
-      <c r="H3" s="5">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>18</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>18</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1868064651842765</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1174892122467159</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2194096613494999</v>
-      </c>
-      <c r="E3" s="4">
-        <v>29.16326530612245</v>
-      </c>
-      <c r="F3" s="4">
-        <v>54.25458612975378</v>
-      </c>
-      <c r="G3" s="5">
-        <v>25</v>
-      </c>
-      <c r="H3" s="5">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>14</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>12</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/JiangModelling2021.xlsx
+++ b/public/downloads/JiangModelling2021.xlsx
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06069019570808993</v>
+        <v>-0.04852196791969421</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1359606413606922</v>
+        <v>0.1354739122491564</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03072176512878113</v>
+        <v>0.02898344687329603</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -1787,16 +1787,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1174892122467159</v>
+        <v>-0.1226913982555251</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1565018064796635</v>
+        <v>0.1562937190393112</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06650123187085689</v>
+        <v>0.06602830587005606</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -1969,16 +1969,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.05082321189869132</v>
+        <v>0.03377748041597073</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1921688267988733</v>
+        <v>0.1925961944692022</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03265333566829609</v>
+        <v>0.03032990134602631</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -2151,16 +2151,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0831060369197382</v>
+        <v>-0.09836085357356694</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1660903117661232</v>
+        <v>0.1657795710490839</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1159855670425376</v>
+        <v>0.1125057351122068</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2333,13 +2333,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07791603198902752</v>
+        <v>-0.07247647581098282</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09843941183832865</v>
+        <v>0.09865699408545044</v>
       </c>
       <c r="Q3" s="4">
         <v>0.04596941334595215</v>
@@ -2515,16 +2515,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06868355790376279</v>
+        <v>-0.03163768013377011</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1284989233651399</v>
+        <v>0.1190370301588974</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08565917752053435</v>
+        <v>0.08199361028438444</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -2697,16 +2697,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2332502790722853</v>
+        <v>-0.2444786773334342</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09789509623748437</v>
+        <v>0.09861940551147126</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.02852958038640429</v>
+        <v>0.02639955540379364</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -3059,16 +3059,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1182810018005842</v>
+        <v>-0.1490446277519197</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1091525168368696</v>
+        <v>0.1134879739575813</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04703682075704426</v>
+        <v>0.04299353536486228</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3435,13 +3435,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1273865862705376</v>
+        <v>0.127443263423672</v>
       </c>
       <c r="I4" s="4">
-        <v>0.04049534694279968</v>
+        <v>0.04046944148381345</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1272579340322585</v>
+        <v>0.1265660949360561</v>
       </c>
       <c r="K4" s="4">
         <v>28.75782312925169</v>
@@ -3585,13 +3585,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1195192300007945</v>
+        <v>0.1211363615743111</v>
       </c>
       <c r="I7" s="4">
-        <v>0.04066710313548086</v>
+        <v>0.03777378973399455</v>
       </c>
       <c r="J7" s="4">
-        <v>0.07658893911216026</v>
+        <v>0.07976594060298044</v>
       </c>
       <c r="K7" s="4">
         <v>28.90306122448981</v>
@@ -3635,13 +3635,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1359606413606922</v>
+        <v>0.1354739122491564</v>
       </c>
       <c r="I8" s="4">
-        <v>0.03072176512878113</v>
+        <v>0.02898344687329603</v>
       </c>
       <c r="J8" s="4">
-        <v>0.07709624232482215</v>
+        <v>0.07949067238370697</v>
       </c>
       <c r="K8" s="4">
         <v>31.04489795918367</v>
@@ -3685,13 +3685,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.1565018064796635</v>
+        <v>0.1562937190393112</v>
       </c>
       <c r="I9" s="4">
-        <v>0.06650123187085689</v>
+        <v>0.06602830587005606</v>
       </c>
       <c r="J9" s="4">
-        <v>0.1562062804762213</v>
+        <v>0.1554729692549997</v>
       </c>
       <c r="K9" s="4">
         <v>29.16326530612245</v>
@@ -3735,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1921688267988733</v>
+        <v>0.1925961944692022</v>
       </c>
       <c r="I10" s="4">
-        <v>0.03265333566829609</v>
+        <v>0.03032990134602631</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1138221176798819</v>
+        <v>0.1193812299038844</v>
       </c>
       <c r="K10" s="4">
         <v>28.99319727891157</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1660903117661232</v>
+        <v>0.1657795710490839</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1159855670425376</v>
+        <v>0.1125057351122068</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1560887334993542</v>
+        <v>0.1579193114978136</v>
       </c>
       <c r="K11" s="4">
         <v>31.47210884353736</v>
@@ -3835,13 +3835,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.09843941183832865</v>
+        <v>0.09865699408545044</v>
       </c>
       <c r="I12" s="4">
         <v>0.04596941334595215</v>
       </c>
       <c r="J12" s="4">
-        <v>0.07778368301571571</v>
+        <v>0.07716230806090447</v>
       </c>
       <c r="K12" s="4">
         <v>27.20680272108846</v>
@@ -3885,13 +3885,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1284989233651399</v>
+        <v>0.1190370301588974</v>
       </c>
       <c r="I13" s="4">
-        <v>0.08565917752053435</v>
+        <v>0.08199361028438444</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1174183202073245</v>
+        <v>0.1002331971541726</v>
       </c>
       <c r="K13" s="4">
         <v>34.78367346938776</v>
@@ -3935,13 +3935,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.09789509623748437</v>
+        <v>0.09861940551147126</v>
       </c>
       <c r="I14" s="4">
-        <v>0.02852958038640429</v>
+        <v>0.02639955540379364</v>
       </c>
       <c r="J14" s="4">
-        <v>0.08626457267954871</v>
+        <v>0.08581543674910273</v>
       </c>
       <c r="K14" s="4">
         <v>30.88299319727891</v>
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1091525168368696</v>
+        <v>0.1134879739575813</v>
       </c>
       <c r="I16" s="4">
-        <v>0.04703682075704426</v>
+        <v>0.04299353536486228</v>
       </c>
       <c r="J16" s="4">
-        <v>0.0628565911374719</v>
+        <v>0.07459413123151698</v>
       </c>
       <c r="K16" s="4">
         <v>36.66666666666666</v>
@@ -4135,13 +4135,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <v>0.06513474206140693</v>
+        <v>0.06518632000594804</v>
       </c>
       <c r="I18" s="4">
         <v>0.02839242812467254</v>
       </c>
       <c r="J18" s="4">
-        <v>0.05902947614612237</v>
+        <v>0.05918420997974571</v>
       </c>
       <c r="K18" s="4">
         <v>37.0639455782313</v>
@@ -4328,13 +4328,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03098295096032214</v>
+        <v>-0.03141276716483143</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06513474206140693</v>
+        <v>0.06518632000594804</v>
       </c>
       <c r="Q3" s="4">
         <v>0.02839242812467254</v>
@@ -6288,16 +6288,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2984004114507624</v>
+        <v>-0.2999727730330406</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1273865862705376</v>
+        <v>0.127443263423672</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04049534694279968</v>
+        <v>0.04046944148381345</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -6830,16 +6830,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.00902105629404574</v>
+        <v>-0.02052389977737334</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1195192300007945</v>
+        <v>0.1211363615743111</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04066710313548086</v>
+        <v>0.03777378973399455</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
